--- a/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,118 +425,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A17"/>
+  <dimension ref="A2:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hQiNHHd2</t>
+          <t>hIoLKAg0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>C6QBlj7R</t>
+          <t>KEflYcbt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dbI3Q902</t>
+          <t>EyfhXHDn</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zkH7PTF8</t>
+          <t>SvbdWyTh</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UPVAOmVE</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8GUEN7pL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>juKJMRaR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Usy7kWiL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lSHwpAFr</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MNAkH5Nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>S0BoIo8r</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0E9gGPxe</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ik4bFqh1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dt32E377</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vqenBDBt</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SWX9C8ZI</t>
+          <t>trWntSE7</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A7"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>hIoLKAg0</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nmEIaKrM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bush evan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +547,54 @@
           <t>KEflYcbt</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rorJXVFH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>chancalay tomas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>naY5y3Ap</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>yusuf alhassan</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EB1E2JsJ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ostrak tomas</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UZ0eZe4O</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>celio pompeu</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +602,54 @@
           <t>EyfhXHDn</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EHyj8Rwo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mitchell roald</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>A7xP1pMQ</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>agade william</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Krqp3vSl</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ford kortne</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>hQBGGZbN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>russell johnny</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +657,70 @@
           <t>SvbdWyTh</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fRhphq6i</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gasper chase</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tdoa9jx7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>akinmboni matai</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ENyQYY5d</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>antley william</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>pMh10sbj</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>canouse russell</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>U9y2jka5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>hopkins jackson</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ns97bC2n</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>schnegg david</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +728,62 @@
           <t>AoWGqXpJ</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pWWpCLNS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ennali lawrence</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>b7DGETog</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>escobar franco</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AymTlL8c</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>dellavalle lorenzo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SQqkeCBr</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>murillo jesus</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WWqBvVIo</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>palencia sergi</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +791,369 @@
           <t>trWntSE7</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OAVZLEcs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>johnson levonte</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A51V8t9T</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>picault fafa</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6ZmchPft</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>fraser liam</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2BYxcCoI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>geovane jesus</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ngsoZ62f</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>pomykal paxton</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>lEqeFmMG</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>white brian</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A28"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>A3m1Vera</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>QmYwykMP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>hernandez ronald</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8WfhluiD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>westberg quentin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>lzufYFED</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>boyd tyler</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>KGSWnoI0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>leal randall</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>UXv2usbH</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>macnaughton lukas</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>jy2ZAeGH</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>yazbek patrick</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +611,34 @@
           <t>8lOY3V6E</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0l5tduvR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>waterman joel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +646,90 @@
           <t>ITj9TZCB</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tdoa9jx7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>akinmboni matai</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ENyQYY5d</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>antley william</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hfXWRScD</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fernandez julian</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Qo2F3mDP</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>jones malachi</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>tx4wbOZQ</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>perea andreas</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>U9y2jka5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>hopkins jackson</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>23FbWu7B</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>klich mateusz</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ns97bC2n</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>schnegg david</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +737,90 @@
           <t>lfn5UFc5</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hxvYvgmQ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>foster isaiah</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>G8J0E6NO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hagglund nick</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nmEIaKrM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>bush evan</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vPaIjQ6l</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>romero abraham</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>YHNlP88c</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>kann alec</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>xtm44hb9</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>miazga matthew</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Ac0f6aUi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>murphy ian</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>S0jteiei</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>robinson miles</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +828,50 @@
           <t>dKkDSgSH</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4nPbkFeS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>farias facundo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>drwnu3ZE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>freire nicolas</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ewo9UCjb</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>leflore isaiah</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +879,42 @@
           <t>vquIRDsO</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MN3tNIu1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cartagena wilder</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>rorJXVFH</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>chancalay tomas</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +922,42 @@
           <t>jDDw3kMK</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>zwOGJAV1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>flores deybi</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6woPNf9c</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>guilherme biro</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +965,50 @@
           <t>xUcLQXdU</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fRhphq6i</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gasper chase</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IehILnUA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>forsberg emil</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>EHyj8Rwo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>mitchell roald</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1016,74 @@
           <t>EkZQoHSu</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pWWpCLNS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ennali lawrence</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>b7DGETog</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>escobar franco</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>APPpO179</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>bonilla jose</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>fZM0WV7l</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ruiz pablo</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SdBJUCMo</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>quinones nelson</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>nydehH4r</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>segal gabriel</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +1091,50 @@
           <t>htYUpyrn</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>tK4wpiO8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>nilsson joakim</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EB1E2JsJ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ostrak tomas</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>UZ0eZe4O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>celio pompeu</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +1142,50 @@
           <t>AHSZqech</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>xnxAyHsn</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rafael navarro</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>G6wRoa8r</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yapi darren</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>COWIPrGB</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>loria marvin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +1193,50 @@
           <t>l8RwqFCb</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nwVf51UA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>paintsil joseph</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AymTlL8c</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>dellavalle lorenzo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SQqkeCBr</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>murillo jesus</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +1244,66 @@
           <t>foKU4Bi8</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>vZHlFq0T</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>anchor max</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lEqeFmMG</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>white brian</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2iyO8h24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>gruezo carlos</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>v5gGA3R2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>marcinkowski jt</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>08UQE1DR</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ricketts jamar</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,97 +1311,82 @@
           <t>rVQsrZR4</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYUosgsB</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>U3Cs29yR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>vcKjtDdH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Me49cTqr</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>ImJfuXBN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0n3Ddmal</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM4QZAZp</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>URr9bfCo</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>QDIbviRT</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rVnDcERi</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xhnHdYtb</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>GroLehd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YJuQfCBA</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IkRCT4d9</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>frei stefan</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>O4TX4LC9</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>joao paulo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>fNA0X55t</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>davis jake</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0GwTHQvo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>fernandez joaquin</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Krqp3vSl</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ford kortne</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>p0TRjzSa</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>radoja nemanja</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>06BxDxL0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ruidiaz raul</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,113 +491,121 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>QmYwykMP</t>
+          <t>Qo2F3mDP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hernandez ronald</t>
+          <t>jones malachi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8WfhluiD</t>
+          <t>UyiqLYVE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>westberg quentin</t>
+          <t>tanasijevic strahinja</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>lzufYFED</t>
+          <t>KUlXbpuK</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>boyd tyler</t>
+          <t>allen noah</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KGSWnoI0</t>
+          <t>ltO3zYt1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>leal randall</t>
+          <t>campana leonardo</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UXv2usbH</t>
+          <t>4nPbkFeS</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>macnaughton lukas</t>
+          <t>farias facundo</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>jy2ZAeGH</t>
+          <t>drwnu3ZE</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>yazbek patrick</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>freire nicolas</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>OMbO44MM</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>rojas matias</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -608,25 +616,33 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0l5tduvR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>waterman joel</t>
-        </is>
-      </c>
+          <t>6XwYhjtN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>rorJXVFH</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>chancalay tomas</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>YueP3mZg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>sands will</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -643,231 +659,167 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tdoa9jx7</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>akinmboni matai</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ENyQYY5d</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>antley william</t>
-        </is>
-      </c>
+          <t>rBhIe7Ef</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hfXWRScD</t>
+          <t>AuWO1Jom</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>fernandez julian</t>
+          <t>czichos rafael</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Qo2F3mDP</t>
+          <t>fRhphq6i</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>jones malachi</t>
+          <t>gasper chase</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>tx4wbOZQ</t>
+          <t>QJrUSjEf</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>perea andreas</t>
+          <t>gutman andrew</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>U9y2jka5</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>hopkins jackson</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>23FbWu7B</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>klich mateusz</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>ns97bC2n</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>schnegg david</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hxvYvgmQ</t>
+          <t>nmEIaKrM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>foster isaiah</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>G8J0E6NO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>hagglund nick</t>
-        </is>
-      </c>
+          <t>bush evan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nmEIaKrM</t>
+          <t>bF92gq0b</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>bush evan</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>vPaIjQ6l</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>romero abraham</t>
-        </is>
-      </c>
+          <t>stajduhar mason</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>YHNlP88c</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>kann alec</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>xtm44hb9</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>miazga matthew</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Ac0f6aUi</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>murphy ian</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>S0jteiei</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>robinson miles</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4nPbkFeS</t>
+          <t>jkAB9GIq</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>farias facundo</t>
+          <t>duncan kyle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>drwnu3ZE</t>
+          <t>IehILnUA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>freire nicolas</t>
+          <t>forsberg emil</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ewo9UCjb</t>
+          <t>QmYwykMP</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>leflore isaiah</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>hernandez ronald</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>jLbdGy1R</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>silva xande</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8WfhluiD</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>westberg quentin</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>EHyj8Rwo</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>mitchell roald</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -876,39 +828,63 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MN3tNIu1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>cartagena wilder</t>
-        </is>
-      </c>
+          <t>2uJ8nlJj</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rorJXVFH</t>
+          <t>pWWpCLNS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>chancalay tomas</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>ennali lawrence</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SdBJUCMo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>quinones nelson</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nydehH4r</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>segal gabriel</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CI6nUjib</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>valdez xavier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OMcrz4wc</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>valverde jefferson</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -919,33 +895,49 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>zwOGJAV1</t>
+          <t>2BYxcCoI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flores deybi</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>geovane jesus</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ngsoZ62f</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>pomykal paxton</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6woPNf9c</t>
+          <t>AymTlL8c</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>guilherme biro</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>dellavalle lorenzo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SQqkeCBr</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>murillo jesus</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -962,124 +954,140 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fRhphq6i</t>
+          <t>lzufYFED</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gasper chase</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>boyd tyler</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>UXv2usbH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>macnaughton lukas</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IehILnUA</t>
+          <t>Wb24z4qm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>forsberg emil</t>
+          <t>bucha pavel</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>EHyj8Rwo</t>
+          <t>hxvYvgmQ</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>mitchell roald</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>foster isaiah</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>G8J0E6NO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>hagglund nick</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>YHNlP88c</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>kann alec</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>xtm44hb9</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>miazga matthew</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>EmByTsz3</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>yedlin deandre</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pWWpCLNS</t>
+          <t>Krqp3vSl</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ennali lawrence</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>b7DGETog</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>escobar franco</t>
-        </is>
-      </c>
+          <t>ford kortne</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>APPpO179</t>
+          <t>dUHOzpD6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>bonilla jose</t>
+          <t>irwin clinton</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>fZM0WV7l</t>
+          <t>xU6utcN5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ruiz pablo</t>
+          <t>valentin zarek</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>SdBJUCMo</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>quinones nelson</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>nydehH4r</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>segal gabriel</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1088,47 +1096,31 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>tK4wpiO8</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>nilsson joakim</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>EB1E2JsJ</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ostrak tomas</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>tdBLfRT0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AH6Dnzt9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>long kevin</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>UZ0eZe4O</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>celio pompeu</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1139,39 +1131,31 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>xnxAyHsn</t>
+          <t>APPpO179</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rafael navarro</t>
+          <t>bonilla jose</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>G6wRoa8r</t>
+          <t>fZM0WV7l</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yapi darren</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>COWIPrGB</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>loria marvin</t>
-        </is>
-      </c>
+          <t>ruiz pablo</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1190,41 +1174,41 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nwVf51UA</t>
+          <t>tQFQdOTG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>paintsil joseph</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>aude julian bernardi</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2T435VVE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>caceres martin</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AymTlL8c</t>
+          <t>zP3uNOEs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>dellavalle lorenzo</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>SQqkeCBr</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>murillo jesus</t>
-        </is>
-      </c>
+          <t>ahmed ali</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1241,152 +1225,85 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>vZHlFq0T</t>
+          <t>v5Rs2UJm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>anchor max</t>
+          <t>ebobisse jeremy</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>lEqeFmMG</t>
+          <t>jLvCo8Tr</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>white brian</t>
+          <t>espinoza cristian</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2iyO8h24</t>
+          <t>tK4wpiO8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>gruezo carlos</t>
+          <t>nilsson joakim</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>v5gGA3R2</t>
+          <t>EB1E2JsJ</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>marcinkowski jt</t>
+          <t>ostrak tomas</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>08UQE1DR</t>
+          <t>UZ0eZe4O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ricketts jamar</t>
+          <t>celio pompeu</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>v5gGA3R2</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>marcinkowski jt</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>IkRCT4d9</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>frei stefan</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>O4TX4LC9</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>joao paulo</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>fNA0X55t</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>davis jake</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0GwTHQvo</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>fernandez joaquin</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Krqp3vSl</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>ford kortne</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>p0TRjzSa</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>radoja nemanja</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>06BxDxL0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ruidiaz raul</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Ec27trNj</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>wilson bruno</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,519 +425,3367 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:CW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_10</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>YuZ4CywD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qo2F3mDP</t>
+          <t>M3Uze1K2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jones malachi</t>
+          <t>guzan brad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UyiqLYVE</t>
+          <t>QmYwykMP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tanasijevic strahinja</t>
+          <t>hernandez ronald</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KUlXbpuK</t>
+          <t>vPRl0Icq</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>allen noah</t>
+          <t>gregersen stian</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ltO3zYt1</t>
+          <t>4U2YRBhO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>campana leonardo</t>
+          <t>williams derrick</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4nPbkFeS</t>
+          <t>2BzWQRsG</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>farias facundo</t>
+          <t>amador pedro miguel santos</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>drwnu3ZE</t>
+          <t>Mc2UiGHB</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>freire nicolas</t>
+          <t>slisz bartosza</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>OMbO44MM</t>
+          <t>vPHmMOvg</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>rojas matias</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+          <t>fortune ajani</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SEHVGTmg</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>lobjanidze saba</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2Dqy3eXn</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>miranchuk aleksey</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>vPuxSnSS</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>mosquera edwin</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>ULIarm52</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>thiare jamal</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>U1vy4HGk</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>carlos coronel</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>lrm5HUGk</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>nealis sean</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>rXSckKil</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>reyes andres</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>21LF2F5n</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>eile noah</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>KhShc534</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>tolkin john</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>AwQIIHlp</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>harper cameron</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>8lSe4DC8</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>donkor ronald</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>M3OWSmEK</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>edelman daniel</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>lAPySJyI</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>carballo felipe</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>r98Hclis</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>vanzeir dante</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>hfxD47ea</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>morgan lewis</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>8xa2tgyo</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>abram luis</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>h6iFwnem</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>brennan luke</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>EF2LTLFO</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>cobb noah</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>A5qnVvGT</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>cohen josh</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>O8hSmb4T</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>edwards matthew</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>r1ZFqEYf</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>mccarty dax</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>8EQU2DNn</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>nick firmino</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>WSg3ZNRK</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>rios daniel</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Cj6yFHA1</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>wolff tyler</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>r9KSzxIr</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>elias manoel</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>IehILnUA</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>forsberg emil</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>Kx11bv9D</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>gjengaar dennis</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>lCyxppgD</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>hall julian</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>I7hHvjo8</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>meara ryan</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>2opOliMF</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>nealis dylan</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>Chep7XVi</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>ngoma serge</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>CKmY1Xij</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>o connor aidan</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2RlHwfAS</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>stroud peter</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>lEm6FVi5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>lennon brooks</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>dAeQdaOl</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>muyumba tristan</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>jLbdGy1R</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>silva xande</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>8WfhluiD</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>westberg quentin</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>S88XrqYl</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>carmona wikelman</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>jkAB9GIq</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>duncan kyle</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>EHyj8Rwo</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>mitchell roald</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>UuWb8pb0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tCYRfWGU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>kahlina kristijan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2Hk6Qxu3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>byrne nathan</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rorJXVFH</t>
+          <t>YuF9dYaN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>chancalay tomas</t>
+          <t>malanda adilson</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>YueP3mZg</t>
+          <t>d4Zg8Fa2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>sands will</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+          <t>privett andrew</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>rcZZwu8e</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ream tim</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Y7GqEIyO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>junior urso</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>lSODVH6K</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>bronico brandt</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>QRAVRj9f</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>biel pep</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Gd5hqV7h</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>westwood ashley</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>lObMfPz8</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>abada liel</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>zkCQVwVh</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>swiderski karol</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M9zBEjDs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>sirois jonathan</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>YsPPQKfU</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>campbell george</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0l5tduvR</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>waterman joel</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>xA02MROI</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>corbo gabriele</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>rD6gr7yH</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>marshall rutty jahkeele</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>63QJMufq</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>piette samuel</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ALAGXH2B</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>saliba nathan</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>zDdlwQJ0</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>edwards raheem</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>YZqwyK64</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>duke bryce</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>SSiBigxc</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>clark caden</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>KGKRFdYJ</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>sanusi ibrahim</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>69kPHWm8</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>agyemang patrick</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>tfH0qS7U</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>bingham david</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>rDL1Od4c</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>vargas kerwin</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>Sdv3ugJ7</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>diani djibril</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>ngTfCVJB</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>lindsey jaylin</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>EJRKgLwt</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>paterson jamie</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0lxxpom1</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>tavares iuri</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>4zv75ECa</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>tuiloma bill</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>U7yFa7e2</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>uronen jere</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>UmKMb5IL</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>alvarez fernando</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>zRliyd8M</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>biello alessandro</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>hfSJRB5U</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>breza sebastian</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>AkUK0mtc</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>bugaj dawid</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>I7xyHiFB</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>coccaro matias</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>tfzJeW8h</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>martinez josef</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>4fY0EIz8</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>opoku kwadwo</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>fZtjgR0f</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>pearce tom</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>GxeZPglE</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>sosa joaquin</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>tzFB24Wg</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>forbes jahlane</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>8WHyJFeb</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>petkovic nikola</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>UPOhwmAe</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>lappalainen lassi</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>llHizuVJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IJv9ax1Q</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>schulte patrick</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bgp40b4S</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>jones dejuan</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AuWO1Jom</t>
+          <t>f5qxQepJ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>czichos rafael</t>
+          <t>cheberko yevgen</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>fRhphq6i</t>
+          <t>IVdZK6M8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>gasper chase</t>
+          <t>amundsen malte</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>QJrUSjEf</t>
+          <t>AqWyTfI5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>gutman andrew</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+          <t>farsi mohamed</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>zNRMXJu4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>chambost dylan</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SOGHjAs1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>nagbe darlington</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>EiXH22mt</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>herrera marcelo</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>nmxk6R3j</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ramirez christian</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>f3AIj6Gd</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>rossi diego</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>65KF7LTO</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>cucho hernandez</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>ABzjRFre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>blake andre</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>6BLphg38</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>harriel nathan</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>QyCyxm0g</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>glesnes jakob</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>8CN7Nng2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>elliott jack</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>O6htidEe</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>wagner kai</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>ADHNs0BF</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>jean jacques danley</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tlilbW9M</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>sullivan quinn</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>pK1XzKbU</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>flach leon</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>dlj9zaWb</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>gazdag daniel</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>259hPT4F</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>baribo tai</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>8643FysN</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>uhre mikael</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>Y7TZabC7</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>arfsten maximilian</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>2uFgW9QP</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>habroune taha</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>hGBjyLfE</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>hagen nicholas</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>U3UI3wS3</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>jackson aziel</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>KMj0M58F</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>johnson cole</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>A70Jf46M</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>jones derrick</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>A9cyouqp</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>matan alexandru</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>dzTXj2Mu</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>russell rowe jacen</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>lMqsisyG</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>yeboah yaw</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>jJ0Bn0VE</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>adeniran samuel</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>UsBqE6t9</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>bedoya alejandro</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>MBaUW69d</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>bueno jesus</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>EFptvtls</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>donovan chris</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>08Tn3g3J</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>mbaizo olivier</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>QqD1LqEi</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>mcglynn jack</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>I17X8gpH</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>rafanello jeremy</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>fyVC7jve</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>rick andrew</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>zBzH8JUb</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>sullivan cavan</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>nmEIaKrM</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>bush evan</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>QganPGYI</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>camacho rudy</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>rH3tj2lb</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>zawadzki sean</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>Ewo9UCjb</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>leflore isaiah</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>CWX8BehJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nmEIaKrM</t>
+          <t>65qMcSsk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bush evan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>celentano roman</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EeCZfvc1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>powell alvas</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>S0jteiei</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>robinson miles</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6uqNPSM3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hadebe teenage</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EmByTsz3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>yedlin deandre</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Wb24z4qm</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bucha pavel</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Qgy2DEEi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>nwobodo obinna</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ew6ZM870</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>asad yamil</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>UHAYgN9J</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>acosta luciano</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>bgmn5guC</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>kelsy kevin</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>8nQofL4k</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>gioacchini nicholas</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Ik9rz2Bn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>gallese pedro</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0Mh1aQx6</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>smith kyle</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>t65vhYRg</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>schlegel rodrigo</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>8OM9Vfod</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>jansson robin</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>6eXjEYkT</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>rafael santos</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>lhAqDO8D</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>torres facundo</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>lOFDt82b</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>araujo cesar</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>MN3tNIu1</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>cartagena wilder</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2wLx0Osd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>angulo ivan</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>KCeKofNN</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>enrique ramiro</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>ltpb2uSG</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>muriel luis</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>29yL8IQ9</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>baird corey</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>x4GDtQAg</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>halsey bret</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>CM9lhfg0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>keller kipp</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>xSjv8o7m</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>kubo yuya</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>6q7PrXhp</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>louro evan</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>Ac0f6aUi</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>murphy ian</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>CERONUR9</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>orellano luca</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>QJXMi0b1</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>pinto malik</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>SYf84XxQ</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>valenzuela gerado</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>G4Mt1XGo</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>gikling bruseth heine</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>4MsxRhmb</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>felipe martins</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>GxlXiF6D</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>halliday michael</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>xjFz7K56</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>lodeiro nicolas</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>CzMMXwgt</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>lynn jack</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>zLUoizhj</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>ojeda martin</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>ncdGec7l</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>otero javier</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>SfLPuXpT</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>petrasso luca</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>Oh6DMkYH</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>tsukada yutaro</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>ljFQolPh</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>awaziem chidozie</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>hxvYvgmQ</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>foster isaiah</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>G8J0E6NO</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>hagglund nick</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>YHNlP88c</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>kann alec</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>lGn3Qr31</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>brekalo david</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
           <t>bF92gq0b</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>stajduhar mason</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>bBmS5UX8</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>thorhallsson dagur</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>xtm44hb9</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>miazga matthew</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>nurCNCMA</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>santos sergio</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>pK2NUIhs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jkAB9GIq</t>
+          <t>t2qaKiy1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>duncan kyle</t>
+          <t>ivacic aljaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IehILnUA</t>
+          <t>G6fhkE8g</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>forsberg emil</t>
+          <t>bye brandon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>QmYwykMP</t>
+          <t>rgEPHjOC</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>hernandez ronald</t>
+          <t>arreaga xavier</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>jLbdGy1R</t>
+          <t>jqg8GNsP</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>silva xande</t>
+          <t>romney david</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8WfhluiD</t>
+          <t>r55LmW9c</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>westberg quentin</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>miller peyton</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>naY5y3Ap</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>yusuf alhassan</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>vDPZngKJ</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>polster matt</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>EHyj8Rwo</t>
+          <t>Mu4nVXta</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>mitchell roald</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+          <t>langoni luca</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>W8ixgd70</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>gil carles</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>hfGr3JtE</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>boateng ema</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>AeAZMqTq</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>vrioni giacomo</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>INEwm8xA</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>bono alex</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>ENuOM4Jq</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>stroud jared</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>67iee5Vo</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>herrera aaron</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>GjDwWCMo</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>bartlett lucas allen</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>r1rFiuNe</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>peltola matti</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>h0XExJmo</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>santos pedro</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>23FbWu7B</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>klich mateusz</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>6wv4vfJ4</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>rodriguez martin</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>OUH3RyFt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>gabriel pirani</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>bu7kCxIm</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>ku dipietro theodore</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>lAh68Xxm</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>benteke christian</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>GUqdXgyQ</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>bajraktarevic esmir</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>8KDkbY05</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>borrero dylan</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lOgLaOqB</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>edwards earl</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>pfMI4LWA</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>farrell andrew</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>bcUmtA2T</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>gil ignacio</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>tdzmBBpt</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>harkes ian</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>GAO1JDD7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>kaye mark</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>x8DF5hdR</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>lima nick</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>6uFJRXh2</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>parker tim</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>SvwXSrxc</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>badji dominique</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>rsxCgBRR</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>boris enow</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>pMh10sbj</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>canouse russell</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>hG3ZBDF0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>dajome cristian</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>hIw1X6PN</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>murrell jacob</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>WC7nPW78</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>sargis hayden</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>ns97bC2n</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>schnegg david</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>Ielx5NU3</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>tubbs garrison</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>x0okvwyn</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>zamudio luis</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>rorJXVFH</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>chancalay tomas</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>YueP3mZg</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>sands will</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>tdoa9jx7</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>akinmboni matai</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>ENyQYY5d</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>antley william</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>U9y2jka5</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>hopkins jackson</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>nHUd7ayo</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>wood bobby</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>MFWf9Qrf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SMi9jQFn</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>takaoka yohei</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>zmuN7tEa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>laborda mathias</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>pWWpCLNS</t>
+          <t>2eOl9zqa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ennali lawrence</t>
+          <t>veselinovic ranko</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SdBJUCMo</t>
+          <t>neS4MpEa</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>quinones nelson</t>
+          <t>utvik bjorn</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>nydehH4r</t>
+          <t>zP3uNOEs</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>segal gabriel</t>
+          <t>ahmed ali</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CI6nUjib</t>
+          <t>tAgQRmS5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>valdez xavier</t>
+          <t>vite pedro</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>OMcrz4wc</t>
+          <t>EDvdadt9</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>valverde jefferson</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+          <t>cubas andres</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>29H9TmUe</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>adekugbe sam</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>bNMGoy7K</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>armstrong stuart</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AebWyF4I</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>gauld ryan</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>lEqeFmMG</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>white brian</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dKt33vk6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>dayne st clair</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>lvHJtK7r</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>harvey carlos</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>SU4IYPEj</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>diaz jefferson</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>GCVBOWB3</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>tapias miguel</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>ATnYZ2jK</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>markanich anthony</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>p8eIf2uj</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>jeong sang bin</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>jVJw0C0o</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>dotson hassani</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>4jJNjzW1</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>trapp wil</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>nNWUFdAr</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>pereyra joaquin</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>byZFCDEh</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>hlongwane bongokuhle</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>nLnBWjlN</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>tani oluwaseyi</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>f9tMZSaG</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>berhalter sebastian</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>SbZcWdsA</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>blackmon tristan</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>pCOZbM35</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>boehmer isaac</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>OAVZLEcs</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>johnson levonte</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>G6mQcrYu</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>kreilach damir</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>AHvux3a4</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>ocampo edier</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2ytqG7KO</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>mbongue ralph priso</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>S8dyrRb9</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>raposo ryan</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0MWvMpbP</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>schopf alessandro</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>p0fLP0ug</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>bacharach hugo</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>4GtyJ7Ed</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>fragapane franco</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>IRjSH2dO</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>lod robin</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>xnRvKeQq</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>mesanvi loic</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>t6K3dItF</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>padelford devin</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>hW1VSJJd</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>rosales joseph</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>pdsnD8cB</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>shashoua samuel</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>z3GHOxDK</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>smir alec</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>v3tRRPn4</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>yeboah kelvin</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>vZHlFq0T</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>anchor max</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>Cv4ohAAE</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>halbouni belal</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>A51V8t9T</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>picault fafa</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>SxeXIHNo</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>pukki teemu</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>hn0r87gS</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>taylor d j</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>xU6utcN5</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>valentin zarek</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2BYxcCoI</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>geovane jesus</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ngsoZ62f</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>pomykal paxton</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AymTlL8c</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>dellavalle lorenzo</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SQqkeCBr</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>murillo jesus</t>
-        </is>
-      </c>
+          <t>r5LQTx8m</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -950,136 +3798,304 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>KCXGwpBP</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>fontas andreu</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>p0TRjzSa</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>radoja nemanja</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>OhJpD8Re</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>rosero daniel</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>QN2WPSVT</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>thommy erik</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>8h9oZZKj</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>chanot maxime</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>AymTlL8c</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>dellavalle lorenzo</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>SQqkeCBr</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>murillo jesus</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lzufYFED</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>boyd tyler</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>UXv2usbH</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>macnaughton lukas</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Wb24z4qm</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>bucha pavel</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>hxvYvgmQ</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>foster isaiah</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>G8J0E6NO</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>hagglund nick</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>YHNlP88c</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>kann alec</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>xtm44hb9</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>miazga matthew</t>
-        </is>
-      </c>
+          <t>QTAVSdNg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>EmByTsz3</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>yedlin deandre</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>EB1E2JsJ</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>ostrak tomas</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>UZ0eZe4O</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>celio pompeu</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>pWWpCLNS</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>ennali lawrence</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>SdBJUCMo</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>quinones nelson</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>nD7FL7I7</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>steres daniel</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Krqp3vSl</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ford kortne</t>
-        </is>
-      </c>
+          <t>4K9ZRGx0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>dUHOzpD6</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>irwin clinton</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>xU6utcN5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>valentin zarek</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1092,27 +4108,123 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>IoPyEpxl</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>bassett cole</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>6TIvfm8s</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>cabral kevin</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr"/>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>O4TX4LC9</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>joao paulo</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AH6Dnzt9</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>long kevin</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1127,33 +4239,105 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
+      <c r="CH11" t="inlineStr"/>
+      <c r="CI11" t="inlineStr"/>
+      <c r="CJ11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr"/>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>UJe3MKbT</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>obrian jader</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>APPpO179</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bonilla jose</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>fZM0WV7l</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ruiz pablo</t>
-        </is>
-      </c>
+          <t>CpDsQf7C</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -1170,43 +4354,163 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>4lp3AS7N</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>baldisimo michael</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>nczLP774</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>bouda ousseni</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>Cr2jDPjr</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>judd preston</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>GdAkQWX7</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>kikanovic benjamin</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>APPpO179</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>bonilla jose</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>fZM0WV7l</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>ruiz pablo</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>K8nVgpfL</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>vera brayan</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>v5gGA3R2</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
+          <t>marcinkowski jt</t>
+        </is>
+      </c>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>tQFQdOTG</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>aude julian bernardi</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2T435VVE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>caceres martin</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>zP3uNOEs</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ahmed ali</t>
-        </is>
-      </c>
+          <t>SvGeZbpQ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1221,89 +4525,281 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>Qo2F3mDP</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>jones malachi</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>WUxTggeR</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>martins thiago</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>tx4wbOZQ</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>perea andreas</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>0YOF6nEU</t>
+        </is>
+      </c>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>sands james</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>lzufYFED</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>boyd tyler</t>
+        </is>
+      </c>
+      <c r="CN13" t="inlineStr">
+        <is>
+          <t>xnWjT5xI</t>
+        </is>
+      </c>
+      <c r="CO13" t="inlineStr">
+        <is>
+          <t>lovitz daniel</t>
+        </is>
+      </c>
+      <c r="CP13" t="inlineStr">
+        <is>
+          <t>UXv2usbH</t>
+        </is>
+      </c>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>macnaughton lukas</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>v5Rs2UJm</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ebobisse jeremy</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>jLvCo8Tr</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>espinoza cristian</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>tK4wpiO8</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nilsson joakim</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>EB1E2JsJ</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ostrak tomas</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>UZ0eZe4O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>celio pompeu</t>
-        </is>
-      </c>
+          <t>f92nPEMI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>v5gGA3R2</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>marcinkowski jt</t>
-        </is>
-      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Ec27trNj</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>wilson bruno</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>0nxVz5uq</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>toye mason</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
+      <c r="CH14" t="inlineStr"/>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr"/>
+      <c r="CL14" t="inlineStr">
+        <is>
+          <t>6ZmchPft</t>
+        </is>
+      </c>
+      <c r="CM14" t="inlineStr">
+        <is>
+          <t>fraser liam</t>
+        </is>
+      </c>
+      <c r="CN14" t="inlineStr">
+        <is>
+          <t>2BYxcCoI</t>
+        </is>
+      </c>
+      <c r="CO14" t="inlineStr">
+        <is>
+          <t>geovane jesus</t>
+        </is>
+      </c>
+      <c r="CP14" t="inlineStr">
+        <is>
+          <t>ngsoZ62f</t>
+        </is>
+      </c>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>pomykal paxton</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
